--- a/data/datasets/consumption.xlsx
+++ b/data/datasets/consumption.xlsx
@@ -1,78 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SHAD\VKR\data\datasets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC23FB93-A8D8-4057-A915-FC761E0B961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>foods</t>
-  </si>
-  <si>
-    <t>nonfoods</t>
-  </si>
-  <si>
-    <t>services</t>
-  </si>
-  <si>
-    <t>caterings</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,50 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,1753 +424,3863 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F87"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>foods</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nonfoods</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>caterings</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P_foods</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P_nonfoods</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P_services</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>real_foods</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>real_services</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>real_caterings</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>C[t]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="n">
+        <v>43465</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4372.54</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1592.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1719.39</v>
+      </c>
+      <c r="F2" t="n">
+        <v>891.21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>169.78</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1592.16</v>
+      </c>
+      <c r="L2" t="n">
+        <v>891.21</v>
+      </c>
+      <c r="M2" t="n">
+        <v>169.78</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2653.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" s="2" t="n">
+        <v>43496</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3470.37</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1215.82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1291.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>828.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>134.81</v>
+      </c>
+      <c r="H3" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100.64</v>
+      </c>
+      <c r="J3" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1200.572726375037</v>
+      </c>
+      <c r="L3" t="n">
+        <v>818.8371403144469</v>
+      </c>
+      <c r="M3" t="n">
+        <v>133.1193838254172</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2152.529250514901</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="2" t="n">
+        <v>43524</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3411.93</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1195.18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1259.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>827.21</v>
+      </c>
+      <c r="G4" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>102.070033</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100.901664</v>
+      </c>
+      <c r="J4" t="n">
+        <v>101.33226</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1170.941132153842</v>
+      </c>
+      <c r="L4" t="n">
+        <v>816.334304593621</v>
+      </c>
+      <c r="M4" t="n">
+        <v>127.5006935679152</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2114.776130315378</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" s="2" t="n">
+        <v>43555</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3689.41</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1311.02</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1379.37</v>
+      </c>
+      <c r="F5" t="n">
+        <v>860.49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>138.54</v>
+      </c>
+      <c r="H5" t="n">
+        <v>102.6110041749</v>
+      </c>
+      <c r="I5" t="n">
+        <v>101.15391816</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.463991938</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1277.660237848732</v>
+      </c>
+      <c r="L5" t="n">
+        <v>848.0742611879552</v>
+      </c>
+      <c r="M5" t="n">
+        <v>135.0147590056318</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2260.749258042319</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B6" s="2" t="n">
+        <v>43585</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3664.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1368.53</v>
+      </c>
+      <c r="F6" t="n">
+        <v>865.86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="H6" t="n">
+        <v>103.0522314928521</v>
+      </c>
+      <c r="I6" t="n">
+        <v>101.346110604504</v>
+      </c>
+      <c r="J6" t="n">
+        <v>101.6770663210698</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1250.239787470654</v>
+      </c>
+      <c r="L6" t="n">
+        <v>851.5784643764592</v>
+      </c>
+      <c r="M6" t="n">
+        <v>137.4642721927141</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2239.282524039827</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>43465</v>
-      </c>
-      <c r="B2" s="4">
-        <v>4372.54</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1592.16</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1719.39</v>
-      </c>
-      <c r="E2" s="4">
-        <v>891.21</v>
-      </c>
-      <c r="F2" s="4">
-        <v>169.78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>43496</v>
-      </c>
-      <c r="B3" s="4">
-        <v>3470.37</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1215.82</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1291.6500000000001</v>
-      </c>
-      <c r="E3" s="4">
-        <v>828.09</v>
-      </c>
-      <c r="F3" s="4">
-        <v>134.81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>43524</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3411.93</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1195.18</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1259.4100000000001</v>
-      </c>
-      <c r="E4" s="4">
-        <v>827.21</v>
-      </c>
-      <c r="F4" s="4">
-        <v>130.13999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>43555</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3689.41</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1311.02</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1379.37</v>
-      </c>
-      <c r="E5" s="4">
-        <v>860.49</v>
-      </c>
-      <c r="F5" s="4">
-        <v>138.54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>43585</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3664.45</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1288.4000000000001</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1368.53</v>
-      </c>
-      <c r="E6" s="4">
-        <v>865.86</v>
-      </c>
-      <c r="F6" s="4">
-        <v>141.66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="B7" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B7" s="4">
+      <c r="C7" t="n">
         <v>3708.02</v>
       </c>
-      <c r="C7" s="4">
+      <c r="D7" t="n">
         <v>1319.29</v>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" t="n">
         <v>1383.87</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" t="n">
         <v>859.46</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" t="n">
         <v>145.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="H7" t="n">
+        <v>103.4747456419728</v>
+      </c>
+      <c r="I7" t="n">
+        <v>101.5589374367734</v>
+      </c>
+      <c r="J7" t="n">
+        <v>102.0736068797219</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1274.987429845735</v>
+      </c>
+      <c r="L7" t="n">
+        <v>842.0002253988552</v>
+      </c>
+      <c r="M7" t="n">
+        <v>140.5173785138747</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2257.505033758464</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B8" s="4">
+      <c r="C8" t="n">
         <v>3764.54</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D8" t="n">
         <v>1316.86</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E8" t="n">
         <v>1424.2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" t="n">
         <v>874.2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" t="n">
         <v>149.29</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="H8" t="n">
+        <v>102.9780668628913</v>
+      </c>
+      <c r="I8" t="n">
+        <v>101.731587630416</v>
+      </c>
+      <c r="J8" t="n">
+        <v>102.6860485210003</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1278.777161114623</v>
+      </c>
+      <c r="L8" t="n">
+        <v>851.3327882328804</v>
+      </c>
+      <c r="M8" t="n">
+        <v>144.9726184885273</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2275.082567836031</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B9" s="4">
+      <c r="C9" t="n">
         <v>3850.89</v>
       </c>
-      <c r="C9" s="4">
+      <c r="D9" t="n">
         <v>1338.59</v>
       </c>
-      <c r="D9" s="4">
+      <c r="E9" t="n">
         <v>1468.44</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" t="n">
         <v>892.35</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" t="n">
         <v>151.51</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="H9" t="n">
+        <v>102.6691326623026</v>
+      </c>
+      <c r="I9" t="n">
+        <v>101.9045313293877</v>
+      </c>
+      <c r="J9" t="n">
+        <v>103.6410287722456</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1303.790112265646</v>
+      </c>
+      <c r="L9" t="n">
+        <v>861.0007161941312</v>
+      </c>
+      <c r="M9" t="n">
+        <v>147.5711307490479</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2312.361959208825</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="B10" s="4">
+      <c r="C10" t="n">
         <v>3954.66</v>
       </c>
-      <c r="C10" s="4">
+      <c r="D10" t="n">
         <v>1356.97</v>
       </c>
-      <c r="D10" s="4">
+      <c r="E10" t="n">
         <v>1540.48</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" t="n">
         <v>900.29</v>
       </c>
-      <c r="F10" s="4">
-        <v>156.91999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="G10" t="n">
+        <v>156.92</v>
+      </c>
+      <c r="H10" t="n">
+        <v>101.7348435550757</v>
+      </c>
+      <c r="I10" t="n">
+        <v>102.0777690326476</v>
+      </c>
+      <c r="J10" t="n">
+        <v>103.8275826240356</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1333.830133886611</v>
+      </c>
+      <c r="L10" t="n">
+        <v>867.1009930569132</v>
+      </c>
+      <c r="M10" t="n">
+        <v>154.2441060668158</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2355.17523301034</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B11" s="4">
+      <c r="C11" t="n">
         <v>3909.61</v>
       </c>
-      <c r="C11" s="4">
+      <c r="D11" t="n">
         <v>1341.89</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" t="n">
         <v>1514.31</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" t="n">
         <v>886.42</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" t="n">
         <v>166.99</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="H11" t="n">
+        <v>101.2872102434333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>102.2717167938096</v>
+      </c>
+      <c r="J11" t="n">
+        <v>103.5887791840003</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1324.836567988107</v>
+      </c>
+      <c r="L11" t="n">
+        <v>855.7104417897326</v>
+      </c>
+      <c r="M11" t="n">
+        <v>164.8678047293995</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2345.414814507239</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B12" s="4">
+      <c r="C12" t="n">
         <v>3962.59</v>
       </c>
-      <c r="C12" s="4">
+      <c r="D12" t="n">
         <v>1373.71</v>
       </c>
-      <c r="D12" s="4">
+      <c r="E12" t="n">
         <v>1530.86</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" t="n">
         <v>892.54</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" t="n">
         <v>165.49</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="H12" t="n">
+        <v>101.4695272218715</v>
+      </c>
+      <c r="I12" t="n">
+        <v>102.5887591158705</v>
+      </c>
+      <c r="J12" t="n">
+        <v>103.4023193814691</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1353.81531540624</v>
+      </c>
+      <c r="L12" t="n">
+        <v>863.1721274135688</v>
+      </c>
+      <c r="M12" t="n">
+        <v>163.0932995658317</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2380.08074238564</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B13" s="4">
+      <c r="C13" t="n">
         <v>3989.87</v>
       </c>
-      <c r="C13" s="4">
+      <c r="D13" t="n">
         <v>1390.12</v>
       </c>
-      <c r="D13" s="4">
+      <c r="E13" t="n">
         <v>1542.42</v>
       </c>
-      <c r="E13" s="4">
-        <v>897.06</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="F13" t="n">
+        <v>897.0599999999999</v>
+      </c>
+      <c r="G13" t="n">
         <v>160.26</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="H13" t="n">
+        <v>101.9261400943699</v>
+      </c>
+      <c r="I13" t="n">
+        <v>102.824713261837</v>
+      </c>
+      <c r="J13" t="n">
+        <v>103.5160619327887</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1363.850331929508</v>
+      </c>
+      <c r="L13" t="n">
+        <v>866.5901534995082</v>
+      </c>
+      <c r="M13" t="n">
+        <v>157.2315010179143</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2387.671986446931</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B14" s="4">
+      <c r="C14" t="n">
         <v>4608.66</v>
       </c>
-      <c r="C14" s="4">
+      <c r="D14" t="n">
         <v>1672.93</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" t="n">
         <v>1800</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" t="n">
         <v>951.67</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" t="n">
         <v>184.06</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="H14" t="n">
+        <v>102.5886600049833</v>
+      </c>
+      <c r="I14" t="n">
+        <v>102.9686678604035</v>
+      </c>
+      <c r="J14" t="n">
+        <v>103.7645004814274</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1630.716299363629</v>
+      </c>
+      <c r="L14" t="n">
+        <v>917.1441057246136</v>
+      </c>
+      <c r="M14" t="n">
+        <v>179.4155416310722</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2727.275946719315</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B15" s="4">
+      <c r="C15" t="n">
         <v>3670.85</v>
       </c>
-      <c r="C15" s="4">
-        <v>1275.1199999999999</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="D15" t="n">
+        <v>1275.12</v>
+      </c>
+      <c r="E15" t="n">
         <v>1367.38</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" t="n">
         <v>886.42</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" t="n">
         <v>141.93</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
+      <c r="H15" t="n">
+        <v>103.2965217590177</v>
+      </c>
+      <c r="I15" t="n">
+        <v>103.2054957964825</v>
+      </c>
+      <c r="J15" t="n">
+        <v>104.0135352825829</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1234.426850281319</v>
+      </c>
+      <c r="L15" t="n">
+        <v>852.2160097642904</v>
+      </c>
+      <c r="M15" t="n">
+        <v>137.4005606220808</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2224.04342066769</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B16" s="4">
+      <c r="C16" t="n">
         <v>3652.72</v>
       </c>
-      <c r="C16" s="4">
-        <v>1276.4000000000001</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="D16" t="n">
+        <v>1276.4</v>
+      </c>
+      <c r="E16" t="n">
         <v>1356.53</v>
       </c>
-      <c r="E16" s="4">
-        <v>881.44</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="F16" t="n">
+        <v>881.4400000000001</v>
+      </c>
+      <c r="G16" t="n">
         <v>138.34</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
+      <c r="H16" t="n">
+        <v>103.8853119330441</v>
+      </c>
+      <c r="I16" t="n">
+        <v>103.2467779948011</v>
+      </c>
+      <c r="J16" t="n">
+        <v>104.3983853631284</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1228.662624435937</v>
+      </c>
+      <c r="L16" t="n">
+        <v>844.3042456395198</v>
+      </c>
+      <c r="M16" t="n">
+        <v>133.1660823131209</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2206.132952388578</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B17" s="4">
+      <c r="C17" t="n">
         <v>3937.55</v>
       </c>
-      <c r="C17" s="4">
+      <c r="D17" t="n">
         <v>1430.71</v>
       </c>
-      <c r="D17" s="4">
+      <c r="E17" t="n">
         <v>1522.43</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" t="n">
         <v>851.42</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" t="n">
         <v>132.99</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
+      <c r="H17" t="n">
+        <v>104.8826109276013</v>
+      </c>
+      <c r="I17" t="n">
+        <v>103.7423625291761</v>
+      </c>
+      <c r="J17" t="n">
+        <v>104.4923439099552</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1364.106010850163</v>
+      </c>
+      <c r="L17" t="n">
+        <v>814.8156775329862</v>
+      </c>
+      <c r="M17" t="n">
+        <v>126.7989029104174</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2305.720591293567</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B18" s="4">
+      <c r="C18" t="n">
         <v>2774.97</v>
       </c>
-      <c r="C18" s="4">
+      <c r="D18" t="n">
         <v>1229.44</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" t="n">
         <v>914.98</v>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" t="n">
         <v>564.41</v>
       </c>
-      <c r="F18" s="4">
-        <v>66.150000000000006</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
+      <c r="G18" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>106.6865918355561</v>
+      </c>
+      <c r="I18" t="n">
+        <v>104.1988289243045</v>
+      </c>
+      <c r="J18" t="n">
+        <v>104.6177347226472</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1152.384736307845</v>
+      </c>
+      <c r="L18" t="n">
+        <v>539.4974394124584</v>
+      </c>
+      <c r="M18" t="n">
+        <v>62.00404274040535</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1753.886218460709</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="B19" s="4">
+      <c r="C19" t="n">
         <v>2927.02</v>
       </c>
-      <c r="C19" s="4">
+      <c r="D19" t="n">
         <v>1265.47</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" t="n">
         <v>1041.55</v>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" t="n">
         <v>553</v>
       </c>
-      <c r="F19" s="4">
-        <v>66.989999999999995</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
+      <c r="G19" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>106.857290382493</v>
+      </c>
+      <c r="I19" t="n">
+        <v>104.4593259966153</v>
+      </c>
+      <c r="J19" t="n">
+        <v>105.0989763023714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1184.261734010176</v>
+      </c>
+      <c r="L19" t="n">
+        <v>526.1706816334828</v>
+      </c>
+      <c r="M19" t="n">
+        <v>62.69108992022068</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1773.123505563879</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="4">
+      <c r="C20" t="n">
         <v>3389.56</v>
       </c>
-      <c r="C20" s="4">
+      <c r="D20" t="n">
         <v>1331.57</v>
       </c>
-      <c r="D20" s="4">
+      <c r="E20" t="n">
         <v>1340.05</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" t="n">
         <v>635.62</v>
       </c>
-      <c r="F20" s="4">
-        <v>82.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
+      <c r="G20" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>107.0389477761432</v>
+      </c>
+      <c r="I20" t="n">
+        <v>104.8144877050038</v>
+      </c>
+      <c r="J20" t="n">
+        <v>105.2250950739342</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1244.005128661008</v>
+      </c>
+      <c r="L20" t="n">
+        <v>604.0574252305449</v>
+      </c>
+      <c r="M20" t="n">
+        <v>76.9065856029906</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1924.969139494544</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B21" s="4">
+      <c r="C21" t="n">
         <v>3752.63</v>
       </c>
-      <c r="C21" s="4">
+      <c r="D21" t="n">
         <v>1394.38</v>
       </c>
-      <c r="D21" s="4">
+      <c r="E21" t="n">
         <v>1511.63</v>
       </c>
-      <c r="E21" s="4">
+      <c r="F21" t="n">
         <v>734.48</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" t="n">
         <v>112.14</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
+      <c r="H21" t="n">
+        <v>106.9640205126999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>105.1184497193483</v>
+      </c>
+      <c r="J21" t="n">
+        <v>106.2668235151662</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1303.597222053227</v>
+      </c>
+      <c r="L21" t="n">
+        <v>691.1658556305455</v>
+      </c>
+      <c r="M21" t="n">
+        <v>104.8389911509408</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2099.602068834713</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B22" s="4">
+      <c r="C22" t="n">
         <v>3941.49</v>
       </c>
-      <c r="C22" s="4">
+      <c r="D22" t="n">
         <v>1392.32</v>
       </c>
-      <c r="D22" s="4">
+      <c r="E22" t="n">
         <v>1609</v>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" t="n">
         <v>808.5</v>
       </c>
-      <c r="F22" s="4">
-        <v>131.66999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
+      <c r="G22" t="n">
+        <v>131.67</v>
+      </c>
+      <c r="H22" t="n">
+        <v>106.1403975547521</v>
+      </c>
+      <c r="I22" t="n">
+        <v>105.5494353631976</v>
+      </c>
+      <c r="J22" t="n">
+        <v>106.6600107621723</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1311.771985102823</v>
+      </c>
+      <c r="L22" t="n">
+        <v>758.0160495227891</v>
+      </c>
+      <c r="M22" t="n">
+        <v>124.0526727178297</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2193.840707343442</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B23" s="4">
+      <c r="C23" t="n">
         <v>3935.07</v>
       </c>
-      <c r="C23" s="4">
+      <c r="D23" t="n">
         <v>1379.12</v>
       </c>
-      <c r="D23" s="4">
+      <c r="E23" t="n">
         <v>1574.09</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" t="n">
         <v>835.16</v>
       </c>
-      <c r="F23" s="4">
-        <v>146.69999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
+      <c r="G23" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>105.7052219247776</v>
+      </c>
+      <c r="I23" t="n">
+        <v>106.1405122012315</v>
+      </c>
+      <c r="J23" t="n">
+        <v>106.2120387169712</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1304.68483475813</v>
+      </c>
+      <c r="L23" t="n">
+        <v>786.3138774932049</v>
+      </c>
+      <c r="M23" t="n">
+        <v>138.7821692521446</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2229.78088150348</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B24" s="4">
+      <c r="C24" t="n">
         <v>4010.42</v>
       </c>
-      <c r="C24" s="4">
+      <c r="D24" t="n">
         <v>1432.68</v>
       </c>
-      <c r="D24" s="4">
+      <c r="E24" t="n">
         <v>1606.02</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" t="n">
         <v>826.51</v>
       </c>
-      <c r="F24" s="4">
+      <c r="G24" t="n">
         <v>145.22</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
+      <c r="H24" t="n">
+        <v>106.3605943007113</v>
+      </c>
+      <c r="I24" t="n">
+        <v>106.8622676841999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>106.0739630666391</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1347.002627636145</v>
+      </c>
+      <c r="L24" t="n">
+        <v>779.182728829279</v>
+      </c>
+      <c r="M24" t="n">
+        <v>136.5355289285262</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2262.72088539395</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B25" s="4">
+      <c r="C25" t="n">
         <v>3976.77</v>
       </c>
-      <c r="C25" s="4">
+      <c r="D25" t="n">
         <v>1433.11</v>
       </c>
-      <c r="D25" s="4">
+      <c r="E25" t="n">
         <v>1588.01</v>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" t="n">
         <v>819.95</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" t="n">
         <v>135.69</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
+      <c r="H25" t="n">
+        <v>107.7858262643408</v>
+      </c>
+      <c r="I25" t="n">
+        <v>107.4820688367682</v>
+      </c>
+      <c r="J25" t="n">
+        <v>106.1270000481724</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1329.590401325449</v>
+      </c>
+      <c r="L25" t="n">
+        <v>772.6120587859962</v>
+      </c>
+      <c r="M25" t="n">
+        <v>125.8885372063904</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2228.090997317835</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B26" s="4">
-        <v>4646.2299999999996</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="C26" t="n">
+        <v>4646.23</v>
+      </c>
+      <c r="D26" t="n">
         <v>1746.85</v>
       </c>
-      <c r="D26" s="4">
+      <c r="E26" t="n">
         <v>1854.81</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" t="n">
         <v>897.3</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" t="n">
         <v>147.28</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
+      <c r="H26" t="n">
+        <v>109.4349494061852</v>
+      </c>
+      <c r="I26" t="n">
+        <v>107.9119971121153</v>
+      </c>
+      <c r="J26" t="n">
+        <v>106.5727334483747</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1596.245083932271</v>
+      </c>
+      <c r="L26" t="n">
+        <v>841.9602002933181</v>
+      </c>
+      <c r="M26" t="n">
+        <v>134.5822342854538</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2572.787518511043</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B27" s="4">
+      <c r="C27" t="n">
         <v>3813.76</v>
       </c>
-      <c r="C27" s="4">
+      <c r="D27" t="n">
         <v>1365.56</v>
       </c>
-      <c r="D27" s="4">
+      <c r="E27" t="n">
         <v>1476.75</v>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" t="n">
         <v>835.5</v>
       </c>
-      <c r="F27" s="4">
-        <v>135.94999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
+      <c r="G27" t="n">
+        <v>135.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>110.5402423951877</v>
+      </c>
+      <c r="I27" t="n">
+        <v>108.4839306968096</v>
+      </c>
+      <c r="J27" t="n">
+        <v>106.9777098354786</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1235.351009199025</v>
+      </c>
+      <c r="L27" t="n">
+        <v>781.0038196601131</v>
+      </c>
+      <c r="M27" t="n">
+        <v>122.9868842823512</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2139.341713141489</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="B28" s="4">
+      <c r="C28" t="n">
         <v>3796.68</v>
       </c>
-      <c r="C28" s="4">
+      <c r="D28" t="n">
         <v>1348.55</v>
       </c>
-      <c r="D28" s="4">
+      <c r="E28" t="n">
         <v>1448.63</v>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" t="n">
         <v>863.83</v>
       </c>
-      <c r="F28" s="4">
-        <v>135.66999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
+      <c r="G28" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="H28" t="n">
+        <v>111.888833352409</v>
+      </c>
+      <c r="I28" t="n">
+        <v>109.1131374948511</v>
+      </c>
+      <c r="J28" t="n">
+        <v>107.4484117587547</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1205.258790886272</v>
+      </c>
+      <c r="L28" t="n">
+        <v>803.9485980858317</v>
+      </c>
+      <c r="M28" t="n">
+        <v>121.2542806418304</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2130.461669613934</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B29" s="4">
-        <v>4159.8500000000004</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="C29" t="n">
+        <v>4159.85</v>
+      </c>
+      <c r="D29" t="n">
         <v>1462.49</v>
       </c>
-      <c r="D29" s="4">
+      <c r="E29" t="n">
         <v>1622.26</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" t="n">
         <v>926.47</v>
       </c>
-      <c r="F29" s="4">
+      <c r="G29" t="n">
         <v>148.62</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="3">
+      <c r="H29" t="n">
+        <v>112.8063217858987</v>
+      </c>
+      <c r="I29" t="n">
+        <v>109.898752084814</v>
+      </c>
+      <c r="J29" t="n">
+        <v>107.8459708822621</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1296.461028820476</v>
+      </c>
+      <c r="L29" t="n">
+        <v>859.0677912403872</v>
+      </c>
+      <c r="M29" t="n">
+        <v>131.7479354411307</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2287.276755501994</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B30" s="4">
-        <v>4213.0200000000004</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="C30" t="n">
+        <v>4213.02</v>
+      </c>
+      <c r="D30" t="n">
         <v>1464.95</v>
       </c>
-      <c r="D30" s="4">
+      <c r="E30" t="n">
         <v>1653.34</v>
       </c>
-      <c r="E30" s="4">
+      <c r="F30" t="n">
         <v>939.88</v>
       </c>
-      <c r="F30" s="4">
+      <c r="G30" t="n">
         <v>154.85</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
+      <c r="H30" t="n">
+        <v>113.652369199293</v>
+      </c>
+      <c r="I30" t="n">
+        <v>110.6240838485738</v>
+      </c>
+      <c r="J30" t="n">
+        <v>108.083232018203</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1288.97444929737</v>
+      </c>
+      <c r="L30" t="n">
+        <v>869.5890957828763</v>
+      </c>
+      <c r="M30" t="n">
+        <v>136.2488094977287</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2294.812354577974</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="B31" s="4">
-        <v>4250.6400000000003</v>
-      </c>
-      <c r="C31" s="4">
+      <c r="C31" t="n">
+        <v>4250.64</v>
+      </c>
+      <c r="D31" t="n">
         <v>1490.73</v>
       </c>
-      <c r="D31" s="4">
+      <c r="E31" t="n">
         <v>1678.83</v>
       </c>
-      <c r="E31" s="4">
+      <c r="F31" t="n">
         <v>923.33</v>
       </c>
-      <c r="F31" s="4">
+      <c r="G31" t="n">
         <v>157.75</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
+      <c r="H31" t="n">
+        <v>114.7434319436062</v>
+      </c>
+      <c r="I31" t="n">
+        <v>111.4427020690532</v>
+      </c>
+      <c r="J31" t="n">
+        <v>108.5587982390831</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1299.185473842773</v>
+      </c>
+      <c r="L31" t="n">
+        <v>850.5344706990176</v>
+      </c>
+      <c r="M31" t="n">
+        <v>137.4806359962552</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2287.200580538046</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B32" s="4">
+      <c r="C32" t="n">
         <v>4305.71</v>
       </c>
-      <c r="C32" s="4">
+      <c r="D32" t="n">
         <v>1505.49</v>
       </c>
-      <c r="D32" s="4">
+      <c r="E32" t="n">
         <v>1701.21</v>
       </c>
-      <c r="E32" s="4">
+      <c r="F32" t="n">
         <v>942.66</v>
       </c>
-      <c r="F32" s="4">
-        <v>156.36000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
+      <c r="G32" t="n">
+        <v>156.36</v>
+      </c>
+      <c r="H32" t="n">
+        <v>115.4777899080453</v>
+      </c>
+      <c r="I32" t="n">
+        <v>112.2005124431228</v>
+      </c>
+      <c r="J32" t="n">
+        <v>109.3838451057001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1303.705241673588</v>
+      </c>
+      <c r="L32" t="n">
+        <v>861.7908787984969</v>
+      </c>
+      <c r="M32" t="n">
+        <v>135.402660654061</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2300.898781126146</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B33" s="4">
-        <v>4409.0600000000004</v>
-      </c>
-      <c r="C33" s="4">
+      <c r="C33" t="n">
+        <v>4409.06</v>
+      </c>
+      <c r="D33" t="n">
         <v>1544.89</v>
       </c>
-      <c r="D33" s="4">
+      <c r="E33" t="n">
         <v>1765.41</v>
       </c>
-      <c r="E33" s="4">
+      <c r="F33" t="n">
         <v>939.15</v>
       </c>
-      <c r="F33" s="4">
-        <v>159.61000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="3">
+      <c r="G33" t="n">
+        <v>159.61</v>
+      </c>
+      <c r="H33" t="n">
+        <v>114.900400958505</v>
+      </c>
+      <c r="I33" t="n">
+        <v>113.0644563889348</v>
+      </c>
+      <c r="J33" t="n">
+        <v>110.3464229426303</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1344.547092188059</v>
+      </c>
+      <c r="L33" t="n">
+        <v>851.0923824764751</v>
+      </c>
+      <c r="M33" t="n">
+        <v>138.9116127259132</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2334.551087390447</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B34" s="4">
+      <c r="C34" t="n">
         <v>4584.2</v>
       </c>
-      <c r="C34" s="4">
+      <c r="D34" t="n">
         <v>1559.88</v>
       </c>
-      <c r="D34" s="4">
+      <c r="E34" t="n">
         <v>1877.28</v>
       </c>
-      <c r="E34" s="4">
-        <v>977.19</v>
-      </c>
-      <c r="F34" s="4">
+      <c r="F34" t="n">
+        <v>977.1900000000001</v>
+      </c>
+      <c r="G34" t="n">
         <v>169.85</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="3">
+      <c r="H34" t="n">
+        <v>114.3144089136166</v>
+      </c>
+      <c r="I34" t="n">
+        <v>113.9689720400463</v>
+      </c>
+      <c r="J34" t="n">
+        <v>110.6995314960467</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1364.55239092278</v>
+      </c>
+      <c r="L34" t="n">
+        <v>882.7408633024767</v>
+      </c>
+      <c r="M34" t="n">
+        <v>148.5814444689555</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2395.874698694212</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B35" s="4">
-        <v>4586.1400000000003</v>
-      </c>
-      <c r="C35" s="4">
+      <c r="C35" t="n">
+        <v>4586.14</v>
+      </c>
+      <c r="D35" t="n">
         <v>1564.02</v>
       </c>
-      <c r="D35" s="4">
+      <c r="E35" t="n">
         <v>1849.6</v>
       </c>
-      <c r="E35" s="4">
+      <c r="F35" t="n">
         <v>990.35</v>
       </c>
-      <c r="F35" s="4">
+      <c r="G35" t="n">
         <v>182.17</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="3">
+      <c r="H35" t="n">
+        <v>115.4461215618614</v>
+      </c>
+      <c r="I35" t="n">
+        <v>114.6983734611026</v>
+      </c>
+      <c r="J35" t="n">
+        <v>110.6995314960467</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1354.761839410885</v>
+      </c>
+      <c r="L35" t="n">
+        <v>894.6288991614813</v>
+      </c>
+      <c r="M35" t="n">
+        <v>157.7965526562837</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2407.18729122865</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B36" s="4">
+      <c r="C36" t="n">
         <v>4648.63</v>
       </c>
-      <c r="C36" s="4">
+      <c r="D36" t="n">
         <v>1635.87</v>
       </c>
-      <c r="D36" s="4">
+      <c r="E36" t="n">
         <v>1847.68</v>
       </c>
-      <c r="E36" s="4">
-        <v>987.81</v>
-      </c>
-      <c r="F36" s="4">
+      <c r="F36" t="n">
+        <v>987.8099999999999</v>
+      </c>
+      <c r="G36" t="n">
         <v>177.26</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="3">
+      <c r="H36" t="n">
+        <v>117.9513023997538</v>
+      </c>
+      <c r="I36" t="n">
+        <v>115.5930207740992</v>
+      </c>
+      <c r="J36" t="n">
+        <v>110.7106014491963</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1386.90287153914</v>
+      </c>
+      <c r="L36" t="n">
+        <v>892.2451753216181</v>
+      </c>
+      <c r="M36" t="n">
+        <v>150.2823592394432</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2429.430406100201</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B37" s="4">
+      <c r="C37" t="n">
         <v>4585.24</v>
       </c>
-      <c r="C37" s="4">
+      <c r="D37" t="n">
         <v>1626.76</v>
       </c>
-      <c r="D37" s="4">
+      <c r="E37" t="n">
         <v>1806</v>
       </c>
-      <c r="E37" s="4">
+      <c r="F37" t="n">
         <v>987.5</v>
       </c>
-      <c r="F37" s="4">
+      <c r="G37" t="n">
         <v>164.97</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="3">
+      <c r="H37" t="n">
+        <v>119.4492839402307</v>
+      </c>
+      <c r="I37" t="n">
+        <v>116.4252905236727</v>
+      </c>
+      <c r="J37" t="n">
+        <v>111.6073573209348</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1361.88342561684</v>
+      </c>
+      <c r="L37" t="n">
+        <v>884.7982997755013</v>
+      </c>
+      <c r="M37" t="n">
+        <v>138.1088228896765</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2384.790548282018</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B38" s="4">
+      <c r="C38" t="n">
         <v>5421.43</v>
       </c>
-      <c r="C38" s="4">
+      <c r="D38" t="n">
         <v>1985.03</v>
       </c>
-      <c r="D38" s="4">
-        <v>2190.8000000000002</v>
-      </c>
-      <c r="E38" s="4">
+      <c r="E38" t="n">
+        <v>2190.8</v>
+      </c>
+      <c r="F38" t="n">
         <v>1057.25</v>
       </c>
-      <c r="F38" s="4">
+      <c r="G38" t="n">
         <v>188.36</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="3">
+      <c r="H38" t="n">
+        <v>121.0737942018178</v>
+      </c>
+      <c r="I38" t="n">
+        <v>117.1704123830242</v>
+      </c>
+      <c r="J38" t="n">
+        <v>111.8975364499693</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1639.520767550371</v>
+      </c>
+      <c r="L38" t="n">
+        <v>944.8376019187064</v>
+      </c>
+      <c r="M38" t="n">
+        <v>155.5745413297471</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2739.932910798825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B39" s="4">
+      <c r="C39" t="n">
         <v>4452.34</v>
       </c>
-      <c r="C39" s="4">
+      <c r="D39" t="n">
         <v>1538.06</v>
       </c>
-      <c r="D39" s="4">
+      <c r="E39" t="n">
         <v>1728.24</v>
       </c>
-      <c r="E39" s="4">
+      <c r="F39" t="n">
         <v>1015.87</v>
       </c>
-      <c r="F39" s="4">
+      <c r="G39" t="n">
         <v>170.16</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="3">
+      <c r="H39" t="n">
+        <v>122.817256838324</v>
+      </c>
+      <c r="I39" t="n">
+        <v>117.9554541459905</v>
+      </c>
+      <c r="J39" t="n">
+        <v>112.747957726989</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1252.315871233547</v>
+      </c>
+      <c r="L39" t="n">
+        <v>901.0096683612267</v>
+      </c>
+      <c r="M39" t="n">
+        <v>138.5473054686425</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2291.872845063416</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="B40" s="4">
+      <c r="C40" t="n">
         <v>4488.84</v>
       </c>
-      <c r="C40" s="4">
+      <c r="D40" t="n">
         <v>1548.53</v>
       </c>
-      <c r="D40" s="4">
+      <c r="E40" t="n">
         <v>1751.5</v>
       </c>
-      <c r="E40" s="4">
+      <c r="F40" t="n">
         <v>1021.25</v>
       </c>
-      <c r="F40" s="4">
+      <c r="G40" t="n">
         <v>167.57</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="3">
+      <c r="H40" t="n">
+        <v>124.7332060450019</v>
+      </c>
+      <c r="I40" t="n">
+        <v>118.8755066883292</v>
+      </c>
+      <c r="J40" t="n">
+        <v>114.022009649304</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1241.473741516204</v>
+      </c>
+      <c r="L40" t="n">
+        <v>895.660410775994</v>
+      </c>
+      <c r="M40" t="n">
+        <v>134.3427346359904</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2271.476886928188</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B41" s="4">
+      <c r="C41" t="n">
         <v>5016.01</v>
       </c>
-      <c r="C41" s="4">
+      <c r="D41" t="n">
         <v>1792.66</v>
       </c>
-      <c r="D41" s="4">
+      <c r="E41" t="n">
         <v>1981.92</v>
       </c>
-      <c r="E41" s="4">
-        <v>1063.6199999999999</v>
-      </c>
-      <c r="F41" s="4">
+      <c r="F41" t="n">
+        <v>1063.62</v>
+      </c>
+      <c r="G41" t="n">
         <v>177.81</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="3">
+      <c r="H41" t="n">
+        <v>133.1277508118305</v>
+      </c>
+      <c r="I41" t="n">
+        <v>132.2490011907663</v>
+      </c>
+      <c r="J41" t="n">
+        <v>118.5714878343112</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1346.571236326103</v>
+      </c>
+      <c r="L41" t="n">
+        <v>897.0284673211448</v>
+      </c>
+      <c r="M41" t="n">
+        <v>133.5634373116734</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2377.163140958922</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B42" s="4">
-        <v>4615.7700000000004</v>
-      </c>
-      <c r="C42" s="4">
+      <c r="C42" t="n">
+        <v>4615.77</v>
+      </c>
+      <c r="D42" t="n">
         <v>1722.64</v>
       </c>
-      <c r="D42" s="4">
+      <c r="E42" t="n">
         <v>1666.47</v>
       </c>
-      <c r="E42" s="4">
+      <c r="F42" t="n">
         <v>1045.73</v>
       </c>
-      <c r="F42" s="4">
+      <c r="G42" t="n">
         <v>180.93</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="3">
+      <c r="H42" t="n">
+        <v>136.94851726013</v>
+      </c>
+      <c r="I42" t="n">
+        <v>132.9499208970773</v>
+      </c>
+      <c r="J42" t="n">
+        <v>119.8402027541384</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1257.87415188139</v>
+      </c>
+      <c r="L42" t="n">
+        <v>872.6036638517689</v>
+      </c>
+      <c r="M42" t="n">
+        <v>132.1153405818395</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2262.593156314999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="B43" s="4">
-        <v>4639.6400000000003</v>
-      </c>
-      <c r="C43" s="4">
+      <c r="C43" t="n">
+        <v>4639.64</v>
+      </c>
+      <c r="D43" t="n">
         <v>1750.28</v>
       </c>
-      <c r="D43" s="4">
+      <c r="E43" t="n">
         <v>1676.05</v>
       </c>
-      <c r="E43" s="4">
+      <c r="F43" t="n">
         <v>1030.48</v>
       </c>
-      <c r="F43" s="4">
+      <c r="G43" t="n">
         <v>182.83</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
+      <c r="H43" t="n">
+        <v>137.7702083636908</v>
+      </c>
+      <c r="I43" t="n">
+        <v>132.8302659682699</v>
+      </c>
+      <c r="J43" t="n">
+        <v>119.4567141053251</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1270.434312895533</v>
+      </c>
+      <c r="L43" t="n">
+        <v>862.6388292343488</v>
+      </c>
+      <c r="M43" t="n">
+        <v>132.7064843491843</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2265.779626479067</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B44" s="4">
+      <c r="C44" t="n">
         <v>4678.49</v>
       </c>
-      <c r="C44" s="4">
+      <c r="D44" t="n">
         <v>1739.64</v>
       </c>
-      <c r="D44" s="4">
+      <c r="E44" t="n">
         <v>1700.35</v>
       </c>
-      <c r="E44" s="4">
-        <v>1052.6500000000001</v>
-      </c>
-      <c r="F44" s="4">
+      <c r="F44" t="n">
+        <v>1052.65</v>
+      </c>
+      <c r="G44" t="n">
         <v>185.85</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
+      <c r="H44" t="n">
+        <v>136.2547360716902</v>
+      </c>
+      <c r="I44" t="n">
+        <v>132.2856618778</v>
+      </c>
+      <c r="J44" t="n">
+        <v>120.507933189452</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1276.755619771405</v>
+      </c>
+      <c r="L44" t="n">
+        <v>873.5109566148778</v>
+      </c>
+      <c r="M44" t="n">
+        <v>136.3989284763029</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2286.665504862585</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B45" s="4">
-        <v>4783.5600000000004</v>
-      </c>
-      <c r="C45" s="4">
+      <c r="C45" t="n">
+        <v>4783.56</v>
+      </c>
+      <c r="D45" t="n">
         <v>1772.86</v>
       </c>
-      <c r="D45" s="4">
+      <c r="E45" t="n">
         <v>1751.4</v>
       </c>
-      <c r="E45" s="4">
+      <c r="F45" t="n">
         <v>1067.75</v>
       </c>
-      <c r="F45" s="4">
+      <c r="G45" t="n">
         <v>191.54</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="3">
+      <c r="H45" t="n">
+        <v>134.1700386097934</v>
+      </c>
+      <c r="I45" t="n">
+        <v>131.7036049655377</v>
+      </c>
+      <c r="J45" t="n">
+        <v>122.2070950474233</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1321.353126502413</v>
+      </c>
+      <c r="L45" t="n">
+        <v>873.7217749801291</v>
+      </c>
+      <c r="M45" t="n">
+        <v>142.7591450257055</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2337.834046508248</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="B46" s="4">
+      <c r="C46" t="n">
         <v>4926.38</v>
       </c>
-      <c r="C46" s="4">
+      <c r="D46" t="n">
         <v>1763.78</v>
       </c>
-      <c r="D46" s="4">
+      <c r="E46" t="n">
         <v>1847.69</v>
       </c>
-      <c r="E46" s="4">
+      <c r="F46" t="n">
         <v>1111.17</v>
       </c>
-      <c r="F46" s="4">
+      <c r="G46" t="n">
         <v>203.73</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="3">
+      <c r="H46" t="n">
+        <v>132.3453260847002</v>
+      </c>
+      <c r="I46" t="n">
+        <v>131.6377531630549</v>
+      </c>
+      <c r="J46" t="n">
+        <v>122.268198594947</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1332.710456938383</v>
+      </c>
+      <c r="L46" t="n">
+        <v>908.7972283627984</v>
+      </c>
+      <c r="M46" t="n">
+        <v>153.938190359374</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2395.445875660555</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B47" s="4">
-        <v>4824.9799999999996</v>
-      </c>
-      <c r="C47" s="4">
+      <c r="C47" t="n">
+        <v>4824.98</v>
+      </c>
+      <c r="D47" t="n">
         <v>1727.47</v>
       </c>
-      <c r="D47" s="4">
+      <c r="E47" t="n">
         <v>1773.71</v>
       </c>
-      <c r="E47" s="4">
+      <c r="F47" t="n">
         <v>1101.82</v>
       </c>
-      <c r="F47" s="4">
+      <c r="G47" t="n">
         <v>221.98</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="3">
+      <c r="H47" t="n">
+        <v>131.8424138455783</v>
+      </c>
+      <c r="I47" t="n">
+        <v>131.8352097927995</v>
+      </c>
+      <c r="J47" t="n">
+        <v>122.8917664077812</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1310.253619918789</v>
+      </c>
+      <c r="L47" t="n">
+        <v>896.5775594305686</v>
+      </c>
+      <c r="M47" t="n">
+        <v>168.3676698000965</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2375.198849149454</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B48" s="4">
+      <c r="C48" t="n">
         <v>4878.46</v>
       </c>
-      <c r="C48" s="4">
+      <c r="D48" t="n">
         <v>1772.08</v>
       </c>
-      <c r="D48" s="4">
+      <c r="E48" t="n">
         <v>1789.38</v>
       </c>
-      <c r="E48" s="4">
+      <c r="F48" t="n">
         <v>1095.8</v>
       </c>
-      <c r="F48" s="4">
+      <c r="G48" t="n">
         <v>221.2</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="3">
+      <c r="H48" t="n">
+        <v>132.2115726043459</v>
+      </c>
+      <c r="I48" t="n">
+        <v>131.8879438767166</v>
+      </c>
+      <c r="J48" t="n">
+        <v>123.1867066471599</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1340.336526593702</v>
+      </c>
+      <c r="L48" t="n">
+        <v>889.5440342752796</v>
+      </c>
+      <c r="M48" t="n">
+        <v>167.3075931574911</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2397.188154026472</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="B49" s="4">
+      <c r="C49" t="n">
         <v>4904.3</v>
       </c>
-      <c r="C49" s="4">
+      <c r="D49" t="n">
         <v>1770.89</v>
       </c>
-      <c r="D49" s="4">
+      <c r="E49" t="n">
         <v>1806.31</v>
       </c>
-      <c r="E49" s="4">
+      <c r="F49" t="n">
         <v>1111.32</v>
       </c>
-      <c r="F49" s="4">
+      <c r="G49" t="n">
         <v>215.79</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="3">
+      <c r="H49" t="n">
+        <v>132.7404188947633</v>
+      </c>
+      <c r="I49" t="n">
+        <v>131.9670766430427</v>
+      </c>
+      <c r="J49" t="n">
+        <v>124.1229256176783</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1334.100053883334</v>
+      </c>
+      <c r="L49" t="n">
+        <v>895.3382257706949</v>
+      </c>
+      <c r="M49" t="n">
+        <v>162.5654053201975</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2392.003684974226</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B50" s="4">
+      <c r="C50" t="n">
         <v>5637.08</v>
       </c>
-      <c r="C50" s="4">
+      <c r="D50" t="n">
         <v>2134.88</v>
       </c>
-      <c r="D50" s="4">
+      <c r="E50" t="n">
         <v>2070.19</v>
       </c>
-      <c r="E50" s="4">
+      <c r="F50" t="n">
         <v>1201.25</v>
       </c>
-      <c r="F50" s="4">
+      <c r="G50" t="n">
         <v>230.75</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="3">
+      <c r="H50" t="n">
+        <v>133.5368614081319</v>
+      </c>
+      <c r="I50" t="n">
+        <v>132.0330601813642</v>
+      </c>
+      <c r="J50" t="n">
+        <v>126.6550333002789</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1598.719617555722</v>
+      </c>
+      <c r="L50" t="n">
+        <v>948.44237034941</v>
+      </c>
+      <c r="M50" t="n">
+        <v>172.7987295543463</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2719.960717459478</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B51" s="4">
-        <v>4828.1400000000003</v>
-      </c>
-      <c r="C51" s="4">
+      <c r="C51" t="n">
+        <v>4828.14</v>
+      </c>
+      <c r="D51" t="n">
         <v>1679.52</v>
       </c>
-      <c r="D51" s="4">
+      <c r="E51" t="n">
         <v>1764.09</v>
       </c>
-      <c r="E51" s="4">
-        <v>1166.8599999999999</v>
-      </c>
-      <c r="F51" s="4">
+      <c r="F51" t="n">
+        <v>1166.86</v>
+      </c>
+      <c r="G51" t="n">
         <v>217.67</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="3">
+      <c r="H51" t="n">
+        <v>135.2995479787192</v>
+      </c>
+      <c r="I51" t="n">
+        <v>132.310329607745</v>
+      </c>
+      <c r="J51" t="n">
+        <v>127.9342491366117</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1241.334524091807</v>
+      </c>
+      <c r="L51" t="n">
+        <v>912.0778899120237</v>
+      </c>
+      <c r="M51" t="n">
+        <v>160.8800644583355</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2314.292478462166</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="B52" s="4">
+      <c r="C52" t="n">
         <v>4804.18</v>
       </c>
-      <c r="C52" s="4">
+      <c r="D52" t="n">
         <v>1678.36</v>
       </c>
-      <c r="D52" s="4">
+      <c r="E52" t="n">
         <v>1727.5</v>
       </c>
-      <c r="E52" s="4">
+      <c r="F52" t="n">
         <v>1190.3</v>
       </c>
-      <c r="F52" s="4">
+      <c r="G52" t="n">
         <v>208.02</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="3">
+      <c r="H52" t="n">
+        <v>136.3684144077511</v>
+      </c>
+      <c r="I52" t="n">
+        <v>132.2044813440588</v>
+      </c>
+      <c r="J52" t="n">
+        <v>128.8553757303953</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1230.754208948699</v>
+      </c>
+      <c r="L52" t="n">
+        <v>923.7488100538931</v>
+      </c>
+      <c r="M52" t="n">
+        <v>152.5426550594082</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2307.045674062</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B53" s="4">
-        <v>5196.1099999999997</v>
-      </c>
-      <c r="C53" s="4">
+      <c r="C53" t="n">
+        <v>5196.11</v>
+      </c>
+      <c r="D53" t="n">
         <v>1825.43</v>
       </c>
-      <c r="D53" s="4">
+      <c r="E53" t="n">
         <v>1901.17</v>
       </c>
-      <c r="E53" s="4">
+      <c r="F53" t="n">
         <v>1241.97</v>
       </c>
-      <c r="F53" s="4">
+      <c r="G53" t="n">
         <v>227.53</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="3">
+      <c r="H53" t="n">
+        <v>136.5456933464812</v>
+      </c>
+      <c r="I53" t="n">
+        <v>132.3895676179405</v>
+      </c>
+      <c r="J53" t="n">
+        <v>130.1052728749802</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1336.863840420085</v>
+      </c>
+      <c r="L53" t="n">
+        <v>954.5885209382906</v>
+      </c>
+      <c r="M53" t="n">
+        <v>166.6328643721106</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2458.085225730486</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B54" s="4">
+      <c r="C54" t="n">
         <v>5182.54</v>
       </c>
-      <c r="C54" s="4">
+      <c r="D54" t="n">
         <v>1823.01</v>
       </c>
-      <c r="D54" s="4">
+      <c r="E54" t="n">
         <v>1909.77</v>
       </c>
-      <c r="E54" s="4">
+      <c r="F54" t="n">
         <v>1222.04</v>
       </c>
-      <c r="F54" s="4">
+      <c r="G54" t="n">
         <v>227.72</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="3">
+      <c r="H54" t="n">
+        <v>136.941675857186</v>
+      </c>
+      <c r="I54" t="n">
+        <v>132.5881519693675</v>
+      </c>
+      <c r="J54" t="n">
+        <v>131.1331045306925</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1331.230970111089</v>
+      </c>
+      <c r="L54" t="n">
+        <v>931.9080825345471</v>
+      </c>
+      <c r="M54" t="n">
+        <v>166.2897715940654</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2429.428824239701</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="B55" s="4">
+      <c r="C55" t="n">
         <v>5297.55</v>
       </c>
-      <c r="C55" s="4">
+      <c r="D55" t="n">
         <v>1867.6</v>
       </c>
-      <c r="D55" s="4">
+      <c r="E55" t="n">
         <v>1969.64</v>
       </c>
-      <c r="E55" s="4">
+      <c r="F55" t="n">
         <v>1226.77</v>
       </c>
-      <c r="F55" s="4">
+      <c r="G55" t="n">
         <v>233.54</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="3">
+      <c r="H55" t="n">
+        <v>136.5171566620287</v>
+      </c>
+      <c r="I55" t="n">
+        <v>133.0389516860633</v>
+      </c>
+      <c r="J55" t="n">
+        <v>132.6149086118893</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1368.033180344914</v>
+      </c>
+      <c r="L55" t="n">
+        <v>925.0619050609641</v>
+      </c>
+      <c r="M55" t="n">
+        <v>171.0700733228481</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2464.165158728727</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B56" s="4">
+      <c r="C56" t="n">
         <v>5411.13</v>
       </c>
-      <c r="C56" s="4">
+      <c r="D56" t="n">
         <v>1889.19</v>
       </c>
-      <c r="D56" s="4">
+      <c r="E56" t="n">
         <v>2046.96</v>
       </c>
-      <c r="E56" s="4">
-        <v>1244.0999999999999</v>
-      </c>
-      <c r="F56" s="4">
+      <c r="F56" t="n">
+        <v>1244.1</v>
+      </c>
+      <c r="G56" t="n">
         <v>230.88</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="3">
+      <c r="H56" t="n">
+        <v>136.5035049463625</v>
+      </c>
+      <c r="I56" t="n">
+        <v>133.5977152831448</v>
+      </c>
+      <c r="J56" t="n">
+        <v>133.715612353368</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1383.986441038518</v>
+      </c>
+      <c r="L56" t="n">
+        <v>930.4074356794164</v>
+      </c>
+      <c r="M56" t="n">
+        <v>169.1385141287923</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2483.532390846727</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="4">
+      <c r="C57" t="n">
         <v>5605.86</v>
       </c>
-      <c r="C57" s="4">
+      <c r="D57" t="n">
         <v>1938.32</v>
       </c>
-      <c r="D57" s="4">
-        <v>2180.6799999999998</v>
-      </c>
-      <c r="E57" s="4">
-        <v>1253.9100000000001</v>
-      </c>
-      <c r="F57" s="4">
+      <c r="E57" t="n">
+        <v>2180.68</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1253.91</v>
+      </c>
+      <c r="G57" t="n">
         <v>232.95</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="3">
+      <c r="H57" t="n">
+        <v>137.1723721205996</v>
+      </c>
+      <c r="I57" t="n">
+        <v>134.8134544922214</v>
+      </c>
+      <c r="J57" t="n">
+        <v>134.3574472926642</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1413.054225158301</v>
+      </c>
+      <c r="L57" t="n">
+        <v>933.2642330340424</v>
+      </c>
+      <c r="M57" t="n">
+        <v>169.8228268555378</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2516.141285047881</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="B58" s="4">
+      <c r="C58" t="n">
         <v>5835.06</v>
       </c>
-      <c r="C58" s="4">
+      <c r="D58" t="n">
         <v>1973.96</v>
       </c>
-      <c r="D58" s="4">
+      <c r="E58" t="n">
         <v>2323.19</v>
       </c>
-      <c r="E58" s="4">
+      <c r="F58" t="n">
         <v>1299.03</v>
       </c>
-      <c r="F58" s="4">
+      <c r="G58" t="n">
         <v>238.88</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="3">
+      <c r="H58" t="n">
+        <v>137.0900686973273</v>
+      </c>
+      <c r="I58" t="n">
+        <v>136.3503278734327</v>
+      </c>
+      <c r="J58" t="n">
+        <v>133.9275034613277</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1439.900073548132</v>
+      </c>
+      <c r="L58" t="n">
+        <v>969.9501345331224</v>
+      </c>
+      <c r="M58" t="n">
+        <v>174.2504050584499</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2584.100613139704</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="4">
+      <c r="C59" t="n">
         <v>5733.11</v>
       </c>
-      <c r="C59" s="4">
+      <c r="D59" t="n">
         <v>1933.93</v>
       </c>
-      <c r="D59" s="4">
+      <c r="E59" t="n">
         <v>2254.86</v>
       </c>
-      <c r="E59" s="4">
+      <c r="F59" t="n">
         <v>1287.97</v>
       </c>
-      <c r="F59" s="4">
-        <v>256.35000000000002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="3">
+      <c r="G59" t="n">
+        <v>256.35</v>
+      </c>
+      <c r="H59" t="n">
+        <v>138.2690432881243</v>
+      </c>
+      <c r="I59" t="n">
+        <v>137.8365464472532</v>
+      </c>
+      <c r="J59" t="n">
+        <v>134.7444612324418</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1398.671715671083</v>
+      </c>
+      <c r="L59" t="n">
+        <v>955.8611821365923</v>
+      </c>
+      <c r="M59" t="n">
+        <v>185.3994168932082</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2539.932314700883</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B60" s="4">
+      <c r="C60" t="n">
         <v>5842.15</v>
       </c>
-      <c r="C60" s="4">
+      <c r="D60" t="n">
         <v>1981.7</v>
       </c>
-      <c r="D60" s="4">
-        <v>2304.5300000000002</v>
-      </c>
-      <c r="E60" s="4">
-        <v>1294.1600000000001</v>
-      </c>
-      <c r="F60" s="4">
+      <c r="E60" t="n">
+        <v>2304.53</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1294.16</v>
+      </c>
+      <c r="G60" t="n">
         <v>261.75</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="3">
+      <c r="H60" t="n">
+        <v>140.135675372514</v>
+      </c>
+      <c r="I60" t="n">
+        <v>138.594647452713</v>
+      </c>
+      <c r="J60" t="n">
+        <v>135.3912346463575</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1414.129553186346</v>
+      </c>
+      <c r="L60" t="n">
+        <v>955.8669018569421</v>
+      </c>
+      <c r="M60" t="n">
+        <v>186.7832722140213</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2556.77972725731</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="B61" s="4">
+      <c r="C61" t="n">
         <v>5767.82</v>
       </c>
-      <c r="C61" s="4">
+      <c r="D61" t="n">
         <v>1996.77</v>
       </c>
-      <c r="D61" s="4">
+      <c r="E61" t="n">
         <v>2211.92</v>
       </c>
-      <c r="E61" s="4">
-        <v>1305.1500000000001</v>
-      </c>
-      <c r="F61" s="4">
+      <c r="F61" t="n">
+        <v>1305.15</v>
+      </c>
+      <c r="G61" t="n">
         <v>253.98</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="3">
+      <c r="H61" t="n">
+        <v>142.3077783407879</v>
+      </c>
+      <c r="I61" t="n">
+        <v>139.3291990842124</v>
+      </c>
+      <c r="J61" t="n">
+        <v>137.0565468325077</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1403.134827400851</v>
+      </c>
+      <c r="L61" t="n">
+        <v>952.271183072328</v>
+      </c>
+      <c r="M61" t="n">
+        <v>178.4723245357593</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2533.878335008938</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B62" s="4">
+      <c r="C62" t="n">
         <v>6638.82</v>
       </c>
-      <c r="C62" s="4">
+      <c r="D62" t="n">
         <v>2438.09</v>
       </c>
-      <c r="D62" s="4">
+      <c r="E62" t="n">
         <v>2535.52</v>
       </c>
-      <c r="E62" s="4">
+      <c r="F62" t="n">
         <v>1386.11</v>
       </c>
-      <c r="F62" s="4">
-        <v>279.10000000000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="3">
+      <c r="G62" t="n">
+        <v>279.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>144.4281642380656</v>
+      </c>
+      <c r="I62" t="n">
+        <v>139.9143817203661</v>
+      </c>
+      <c r="J62" t="n">
+        <v>137.1936033793402</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1688.098725662134</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1010.331360834227</v>
+      </c>
+      <c r="M62" t="n">
+        <v>193.2448573811064</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2891.674943877468</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B63" s="4">
+      <c r="C63" t="n">
         <v>5616.17</v>
       </c>
-      <c r="C63" s="4">
+      <c r="D63" t="n">
         <v>1923.67</v>
       </c>
-      <c r="D63" s="4">
-        <v>2110.4699999999998</v>
-      </c>
-      <c r="E63" s="4">
+      <c r="E63" t="n">
+        <v>2110.47</v>
+      </c>
+      <c r="F63" t="n">
         <v>1326.12</v>
       </c>
-      <c r="F63" s="4">
+      <c r="G63" t="n">
         <v>255.91</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="3">
+      <c r="H63" t="n">
+        <v>146.2479591074653</v>
+      </c>
+      <c r="I63" t="n">
+        <v>140.5719793144518</v>
+      </c>
+      <c r="J63" t="n">
+        <v>138.263713485699</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1315.348269979246</v>
+      </c>
+      <c r="L63" t="n">
+        <v>959.123667785159</v>
+      </c>
+      <c r="M63" t="n">
+        <v>174.9836384465053</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2449.45557621091</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="B64" s="4">
+      <c r="C64" t="n">
         <v>5752.28</v>
       </c>
-      <c r="C64" s="4">
+      <c r="D64" t="n">
         <v>1971.02</v>
       </c>
-      <c r="D64" s="4">
-        <v>2152.7199999999998</v>
-      </c>
-      <c r="E64" s="4">
+      <c r="E64" t="n">
+        <v>2152.72</v>
+      </c>
+      <c r="F64" t="n">
         <v>1367.18</v>
       </c>
-      <c r="F64" s="4">
+      <c r="G64" t="n">
         <v>261.36</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
+      <c r="H64" t="n">
+        <v>147.3740683925928</v>
+      </c>
+      <c r="I64" t="n">
+        <v>140.9374664606694</v>
+      </c>
+      <c r="J64" t="n">
+        <v>139.7293088486474</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1337.426605303017</v>
+      </c>
+      <c r="L64" t="n">
+        <v>978.4489820105728</v>
+      </c>
+      <c r="M64" t="n">
+        <v>177.3446325060104</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2493.2202198196</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B65" s="4">
+      <c r="C65" t="n">
         <v>6152.03</v>
       </c>
-      <c r="C65" s="4">
-        <v>2114.0500000000002</v>
-      </c>
-      <c r="D65" s="4">
-        <v>2371.5300000000002</v>
-      </c>
-      <c r="E65" s="4">
+      <c r="D65" t="n">
+        <v>2114.05</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2371.53</v>
+      </c>
+      <c r="F65" t="n">
         <v>1392.68</v>
       </c>
-      <c r="F65" s="4">
+      <c r="G65" t="n">
         <v>273.77</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="3">
+      <c r="H65" t="n">
+        <v>147.6246043088602</v>
+      </c>
+      <c r="I65" t="n">
+        <v>141.3179976201132</v>
+      </c>
+      <c r="J65" t="n">
+        <v>140.8890621120912</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1432.044481946238</v>
+      </c>
+      <c r="L65" t="n">
+        <v>988.4940527831643</v>
+      </c>
+      <c r="M65" t="n">
+        <v>185.4501160438123</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2605.988650773214</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B66" s="4">
+      <c r="C66" t="n">
         <v>6066.07</v>
       </c>
-      <c r="C66" s="4">
+      <c r="D66" t="n">
         <v>2090.63</v>
       </c>
-      <c r="D66" s="4">
+      <c r="E66" t="n">
         <v>2300.62</v>
       </c>
-      <c r="E66" s="4">
+      <c r="F66" t="n">
         <v>1395.42</v>
       </c>
-      <c r="F66" s="4">
-        <v>279.39999999999998</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="3">
+      <c r="G66" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>148.3479648699736</v>
+      </c>
+      <c r="I66" t="n">
+        <v>141.8974014103557</v>
+      </c>
+      <c r="J66" t="n">
+        <v>141.7625742971862</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1409.274472914023</v>
+      </c>
+      <c r="L66" t="n">
+        <v>984.3359623779754</v>
+      </c>
+      <c r="M66" t="n">
+        <v>188.3409726887005</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2581.951407980699</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="B67" s="4">
+      <c r="C67" t="n">
         <v>6198.27</v>
       </c>
-      <c r="C67" s="4">
+      <c r="D67" t="n">
         <v>2166.44</v>
       </c>
-      <c r="D67" s="4">
+      <c r="E67" t="n">
         <v>2340.98</v>
       </c>
-      <c r="E67" s="4">
+      <c r="F67" t="n">
         <v>1408.28</v>
       </c>
-      <c r="F67" s="4">
+      <c r="G67" t="n">
         <v>282.57</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="3">
+      <c r="H67" t="n">
+        <v>148.9561915259405</v>
+      </c>
+      <c r="I67" t="n">
+        <v>142.5501294568433</v>
+      </c>
+      <c r="J67" t="n">
+        <v>143.9315416839331</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1454.414199105458</v>
+      </c>
+      <c r="L67" t="n">
+        <v>978.437376216338</v>
+      </c>
+      <c r="M67" t="n">
+        <v>189.7000702725344</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2622.551645594331</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B68" s="4">
+      <c r="C68" t="n">
         <v>6284.08</v>
       </c>
-      <c r="C68" s="4">
+      <c r="D68" t="n">
         <v>2175.37</v>
       </c>
-      <c r="D68" s="4">
-        <v>2395.9499999999998</v>
-      </c>
-      <c r="E68" s="4">
+      <c r="E68" t="n">
+        <v>2395.95</v>
+      </c>
+      <c r="F68" t="n">
         <v>1425.11</v>
       </c>
-      <c r="F68" s="4">
-        <v>287.66000000000003</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="3">
+      <c r="G68" t="n">
+        <v>287.66</v>
+      </c>
+      <c r="H68" t="n">
+        <v>149.8946155325539</v>
+      </c>
+      <c r="I68" t="n">
+        <v>142.9635248322681</v>
+      </c>
+      <c r="J68" t="n">
+        <v>145.4572160257828</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1451.266272821892</v>
+      </c>
+      <c r="L68" t="n">
+        <v>979.7451367056233</v>
+      </c>
+      <c r="M68" t="n">
+        <v>191.9081609289204</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2622.919570456436</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B69" s="4">
+      <c r="C69" t="n">
         <v>6522.62</v>
       </c>
-      <c r="C69" s="4">
-        <v>2241.2600000000002</v>
-      </c>
-      <c r="D69" s="4">
+      <c r="D69" t="n">
+        <v>2241.26</v>
+      </c>
+      <c r="E69" t="n">
         <v>2519.09</v>
       </c>
-      <c r="E69" s="4">
+      <c r="F69" t="n">
         <v>1467.36</v>
       </c>
-      <c r="F69" s="4">
-        <v>294.91000000000003</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="3">
+      <c r="G69" t="n">
+        <v>294.91</v>
+      </c>
+      <c r="H69" t="n">
+        <v>150.4342361484711</v>
+      </c>
+      <c r="I69" t="n">
+        <v>143.7927132762953</v>
+      </c>
+      <c r="J69" t="n">
+        <v>149.6172924041202</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1489.860325270631</v>
+      </c>
+      <c r="L69" t="n">
+        <v>980.7422500579827</v>
+      </c>
+      <c r="M69" t="n">
+        <v>196.0391514262342</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2666.641726754848</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="B70" s="4">
+      <c r="C70" t="n">
         <v>6702.73</v>
       </c>
-      <c r="C70" s="4">
-        <v>2264.9699999999998</v>
-      </c>
-      <c r="D70" s="4">
+      <c r="D70" t="n">
+        <v>2264.97</v>
+      </c>
+      <c r="E70" t="n">
         <v>2622.9</v>
       </c>
-      <c r="E70" s="4">
+      <c r="F70" t="n">
         <v>1507.46</v>
       </c>
-      <c r="F70" s="4">
-        <v>307.39999999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="3">
+      <c r="G70" t="n">
+        <v>307.4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>150.4191927248562</v>
+      </c>
+      <c r="I70" t="n">
+        <v>144.6554695559531</v>
+      </c>
+      <c r="J70" t="n">
+        <v>149.6322541333606</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1505.771942376421</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1007.443220534837</v>
+      </c>
+      <c r="M70" t="n">
+        <v>204.3622189638326</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2717.577381875091</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B71" s="4">
+      <c r="C71" t="n">
         <v>6578.21</v>
       </c>
-      <c r="C71" s="4">
-        <v>2189.2800000000002</v>
-      </c>
-      <c r="D71" s="4">
+      <c r="D71" t="n">
+        <v>2189.28</v>
+      </c>
+      <c r="E71" t="n">
         <v>2588.67</v>
       </c>
-      <c r="E71" s="4">
+      <c r="F71" t="n">
         <v>1487.24</v>
       </c>
-      <c r="F71" s="4">
+      <c r="G71" t="n">
         <v>313.02</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="3">
+      <c r="H71" t="n">
+        <v>150.9306179801208</v>
+      </c>
+      <c r="I71" t="n">
+        <v>145.5523334672</v>
+      </c>
+      <c r="J71" t="n">
+        <v>150.3953786294408</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1450.520795116835</v>
+      </c>
+      <c r="L71" t="n">
+        <v>988.8867686981336</v>
+      </c>
+      <c r="M71" t="n">
+        <v>207.3933070632681</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2646.800870878236</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B72" s="4">
+      <c r="C72" t="n">
         <v>6625.54</v>
       </c>
-      <c r="C72" s="4">
+      <c r="D72" t="n">
         <v>2241.6</v>
       </c>
-      <c r="D72" s="4">
-        <v>2568.9499999999998</v>
-      </c>
-      <c r="E72" s="4">
+      <c r="E72" t="n">
+        <v>2568.95</v>
+      </c>
+      <c r="F72" t="n">
         <v>1495.97</v>
       </c>
-      <c r="F72" s="4">
-        <v>319.02999999999997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="3">
+      <c r="G72" t="n">
+        <v>319.03</v>
+      </c>
+      <c r="H72" t="n">
+        <v>152.7870645812762</v>
+      </c>
+      <c r="I72" t="n">
+        <v>146.5420893347769</v>
+      </c>
+      <c r="J72" t="n">
+        <v>150.7112089245626</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1467.139908828842</v>
+      </c>
+      <c r="L72" t="n">
+        <v>992.6069936502182</v>
+      </c>
+      <c r="M72" t="n">
+        <v>208.8069437516351</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2668.553846230695</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="B73" s="4">
+      <c r="C73" t="n">
         <v>6606.26</v>
       </c>
-      <c r="C73" s="4">
+      <c r="D73" t="n">
         <v>2271.31</v>
       </c>
-      <c r="D73" s="4">
+      <c r="E73" t="n">
         <v>2518.37</v>
       </c>
-      <c r="E73" s="4">
+      <c r="F73" t="n">
         <v>1505.1</v>
       </c>
-      <c r="F73" s="4">
+      <c r="G73" t="n">
         <v>311.48</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="3">
+      <c r="H73" t="n">
+        <v>156.34700318602</v>
+      </c>
+      <c r="I73" t="n">
+        <v>147.2894539903843</v>
+      </c>
+      <c r="J73" t="n">
+        <v>152.6855257614744</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1452.736511551564</v>
+      </c>
+      <c r="L73" t="n">
+        <v>985.7515913795719</v>
+      </c>
+      <c r="M73" t="n">
+        <v>199.2235179777667</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2637.711620908903</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B74" s="4">
+      <c r="C74" t="n">
         <v>7602.34</v>
       </c>
-      <c r="C74" s="4">
+      <c r="D74" t="n">
         <v>2760.46</v>
       </c>
-      <c r="D74" s="4">
+      <c r="E74" t="n">
         <v>2891.12</v>
       </c>
-      <c r="E74" s="4">
+      <c r="F74" t="n">
         <v>1605.11</v>
       </c>
-      <c r="F74" s="4">
+      <c r="G74" t="n">
         <v>345.65</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="3">
+      <c r="H74" t="n">
+        <v>160.4120252688565</v>
+      </c>
+      <c r="I74" t="n">
+        <v>148.4824985677064</v>
+      </c>
+      <c r="J74" t="n">
+        <v>152.9908968129973</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1720.856023962896</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1049.153925780268</v>
+      </c>
+      <c r="M74" t="n">
+        <v>215.4763643315878</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2985.486314074752</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B75" s="4">
+      <c r="C75" t="n">
         <v>6403.08</v>
       </c>
-      <c r="C75" s="4">
+      <c r="D75" t="n">
         <v>2215.19</v>
       </c>
-      <c r="D75" s="4">
-        <v>2357.7199999999998</v>
-      </c>
-      <c r="E75" s="4">
+      <c r="E75" t="n">
+        <v>2357.72</v>
+      </c>
+      <c r="F75" t="n">
         <v>1530.19</v>
       </c>
-      <c r="F75" s="4">
-        <v>299.97000000000003</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="3">
+      <c r="G75" t="n">
+        <v>299.97</v>
+      </c>
+      <c r="H75" t="n">
+        <v>162.5455052049323</v>
+      </c>
+      <c r="I75" t="n">
+        <v>149.1061250616908</v>
+      </c>
+      <c r="J75" t="n">
+        <v>156.1578083770264</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1362.812215082267</v>
+      </c>
+      <c r="L75" t="n">
+        <v>979.8997667190099</v>
+      </c>
+      <c r="M75" t="n">
+        <v>184.5452444974146</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2527.257226298691</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B76" s="4">
+      <c r="C76" t="n">
         <v>6428.13</v>
       </c>
-      <c r="C76" s="4">
+      <c r="D76" t="n">
         <v>2226.85</v>
       </c>
-      <c r="D76" s="4">
+      <c r="E76" t="n">
         <v>2328.83</v>
       </c>
-      <c r="E76" s="4">
+      <c r="F76" t="n">
         <v>1564.23</v>
       </c>
-      <c r="F76" s="4">
+      <c r="G76" t="n">
         <v>308.23</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="3">
+      <c r="H76" t="n">
+        <v>164.6098331210349</v>
+      </c>
+      <c r="I76" t="n">
+        <v>149.4938009868512</v>
+      </c>
+      <c r="J76" t="n">
+        <v>157.4226866248803</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1352.804967831195</v>
+      </c>
+      <c r="L76" t="n">
+        <v>993.6496660912512</v>
+      </c>
+      <c r="M76" t="n">
+        <v>187.2488381501265</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2533.703472072573</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B77" s="4">
+      <c r="C77" t="n">
         <v>6880.55</v>
       </c>
-      <c r="C77" s="4">
+      <c r="D77" t="n">
         <v>2417.64</v>
       </c>
-      <c r="D77" s="4">
+      <c r="E77" t="n">
         <v>2523.52</v>
       </c>
-      <c r="E77" s="4">
+      <c r="F77" t="n">
         <v>1611.13</v>
       </c>
-      <c r="F77" s="4">
+      <c r="G77" t="n">
         <v>328.27</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="3">
+      <c r="H77" t="n">
+        <v>165.9760947359395</v>
+      </c>
+      <c r="I77" t="n">
+        <v>149.7030923082328</v>
+      </c>
+      <c r="J77" t="n">
+        <v>159.0126557597916</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1456.619402840124</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1013.20866084635</v>
+      </c>
+      <c r="M77" t="n">
+        <v>197.7814940894125</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2667.609557775886</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B78" s="4">
+      <c r="C78" t="n">
         <v>6827.21</v>
       </c>
-      <c r="C78" s="4">
-        <v>2392.5500000000002</v>
-      </c>
-      <c r="D78" s="4">
+      <c r="D78" t="n">
+        <v>2392.55</v>
+      </c>
+      <c r="E78" t="n">
         <v>2465.88</v>
       </c>
-      <c r="E78" s="4">
+      <c r="F78" t="n">
         <v>1631.85</v>
       </c>
-      <c r="F78" s="4">
+      <c r="G78" t="n">
         <v>336.93</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="3">
+      <c r="H78" t="n">
+        <v>167.1545250085647</v>
+      </c>
+      <c r="I78" t="n">
+        <v>149.598300143617</v>
+      </c>
+      <c r="J78" t="n">
+        <v>159.8554228353185</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1431.340252306906</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1020.82867822452</v>
+      </c>
+      <c r="M78" t="n">
+        <v>201.5679802761764</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2653.736910807603</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="B79" s="4">
+      <c r="C79" t="n">
         <v>6937.42</v>
       </c>
-      <c r="C79" s="4">
+      <c r="D79" t="n">
         <v>2468.63</v>
       </c>
-      <c r="D79" s="4">
+      <c r="E79" t="n">
         <v>2495.87</v>
       </c>
-      <c r="E79" s="4">
+      <c r="F79" t="n">
         <v>1621.92</v>
       </c>
-      <c r="F79" s="4">
+      <c r="G79" t="n">
         <v>351</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="3">
+      <c r="H79" t="n">
+        <v>167.5891267735869</v>
+      </c>
+      <c r="I79" t="n">
+        <v>149.4038223534303</v>
+      </c>
+      <c r="J79" t="n">
+        <v>161.9974855013118</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1473.025158329706</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1001.200725419202</v>
+      </c>
+      <c r="M79" t="n">
+        <v>209.4407953292825</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2683.66667907819</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B80" s="4">
+      <c r="C80" t="n">
         <v>6979.02</v>
       </c>
-      <c r="C80" s="4">
+      <c r="D80" t="n">
         <v>2443.77</v>
       </c>
-      <c r="D80" s="4">
-        <v>2543.5300000000002</v>
-      </c>
-      <c r="E80" s="4">
+      <c r="E80" t="n">
+        <v>2543.53</v>
+      </c>
+      <c r="F80" t="n">
         <v>1646.91</v>
       </c>
-      <c r="F80" s="4">
+      <c r="G80" t="n">
         <v>344.81</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="3">
+      <c r="H80" t="n">
+        <v>167.7734748130379</v>
+      </c>
+      <c r="I80" t="n">
+        <v>149.3590012067243</v>
+      </c>
+      <c r="J80" t="n">
+        <v>162.9532706657695</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1456.589012490365</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1010.663973341135</v>
+      </c>
+      <c r="M80" t="n">
+        <v>205.5211650019448</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2672.774150833445</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B81" s="4">
+      <c r="C81" t="n">
         <v>7218.31</v>
       </c>
-      <c r="C81" s="4">
-        <v>2529.2399999999998</v>
-      </c>
-      <c r="D81" s="4">
+      <c r="D81" t="n">
+        <v>2529.24</v>
+      </c>
+      <c r="E81" t="n">
         <v>2668.37</v>
       </c>
-      <c r="E81" s="4">
+      <c r="F81" t="n">
         <v>1665.44</v>
       </c>
-      <c r="F81" s="4">
+      <c r="G81" t="n">
         <v>355.27</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="3">
+      <c r="H81" t="n">
+        <v>166.6997245742345</v>
+      </c>
+      <c r="I81" t="n">
+        <v>149.6427833090171</v>
+      </c>
+      <c r="J81" t="n">
+        <v>167.3367136466787</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1517.243058715243</v>
+      </c>
+      <c r="L81" t="n">
+        <v>995.262763147408</v>
+      </c>
+      <c r="M81" t="n">
+        <v>213.1197282463365</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2725.625550108987</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="B82" s="4">
+      <c r="C82" t="n">
         <v>7443.73</v>
       </c>
-      <c r="C82" s="4">
-        <v>2513.0500000000002</v>
-      </c>
-      <c r="D82" s="4">
+      <c r="D82" t="n">
+        <v>2513.05</v>
+      </c>
+      <c r="E82" t="n">
         <v>2841.06</v>
       </c>
-      <c r="E82" s="4">
+      <c r="F82" t="n">
         <v>1712.97</v>
       </c>
-      <c r="F82" s="4">
+      <c r="G82" t="n">
         <v>376.66</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="3">
+      <c r="H82" t="n">
+        <v>165.1827570806089</v>
+      </c>
+      <c r="I82" t="n">
+        <v>150.271282998915</v>
+      </c>
+      <c r="J82" t="n">
+        <v>166.2992260220693</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1521.375502149801</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1030.052899808851</v>
+      </c>
+      <c r="M82" t="n">
+        <v>228.0262217782154</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2779.454623736868</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B83" s="4">
+      <c r="C83" t="n">
         <v>7268.31</v>
       </c>
-      <c r="C83" s="4">
-        <v>2415.4699999999998</v>
-      </c>
-      <c r="D83" s="4">
+      <c r="D83" t="n">
+        <v>2415.47</v>
+      </c>
+      <c r="E83" t="n">
         <v>2757.34</v>
       </c>
-      <c r="E83" s="4">
+      <c r="F83" t="n">
         <v>1706.91</v>
       </c>
-      <c r="F83" s="4">
+      <c r="G83" t="n">
         <v>388.58</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="3">
+      <c r="H83" t="n">
+        <v>165.2323119077331</v>
+      </c>
+      <c r="I83" t="n">
+        <v>151.1578835686086</v>
+      </c>
+      <c r="J83" t="n">
+        <v>167.080832384373</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1461.862980739999</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1021.607311647345</v>
+      </c>
+      <c r="M83" t="n">
+        <v>235.1719197737703</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2718.642212161115</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B84" s="4">
+      <c r="C84" t="n">
         <v>7472.95</v>
       </c>
-      <c r="C84" s="4">
-        <v>2509.0700000000002</v>
-      </c>
-      <c r="D84" s="4">
+      <c r="D84" t="n">
+        <v>2509.07</v>
+      </c>
+      <c r="E84" t="n">
         <v>2850.9</v>
       </c>
-      <c r="E84" s="4">
+      <c r="F84" t="n">
         <v>1714.65</v>
       </c>
-      <c r="F84" s="4">
+      <c r="G84" t="n">
         <v>398.32</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="3">
+      <c r="H84" t="n">
+        <v>166.9672511827643</v>
+      </c>
+      <c r="I84" t="n">
+        <v>152.1706413885182</v>
+      </c>
+      <c r="J84" t="n">
+        <v>166.3790928883586</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1502.73181251187</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1030.56818632287</v>
+      </c>
+      <c r="M84" t="n">
+        <v>238.5617521869569</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2771.861751021696</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="B85" s="4">
+      <c r="C85" t="n">
         <v>7304.96</v>
       </c>
-      <c r="C85" s="4">
+      <c r="D85" t="n">
         <v>2480.6</v>
       </c>
-      <c r="D85" s="4">
+      <c r="E85" t="n">
         <v>2736.61</v>
       </c>
-      <c r="E85" s="4">
+      <c r="F85" t="n">
         <v>1710.53</v>
       </c>
-      <c r="F85" s="4">
+      <c r="G85" t="n">
         <v>377.23</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="3">
+      <c r="H85" t="n">
+        <v>168.1193252159254</v>
+      </c>
+      <c r="I85" t="n">
+        <v>152.4141144147399</v>
+      </c>
+      <c r="J85" t="n">
+        <v>166.9780576227567</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1475.49961719988</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1024.404059043791</v>
+      </c>
+      <c r="M85" t="n">
+        <v>224.3822948465334</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2724.285971090204</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B86" s="4">
-        <v>8419.7099999999991</v>
-      </c>
-      <c r="C86" s="4">
+      <c r="C86" t="n">
+        <v>8419.709999999999</v>
+      </c>
+      <c r="D86" t="n">
         <v>3008.8</v>
       </c>
-      <c r="D86" s="4">
+      <c r="E86" t="n">
         <v>3158.7</v>
       </c>
-      <c r="E86" s="4">
+      <c r="F86" t="n">
         <v>1835.37</v>
       </c>
-      <c r="F86" s="4">
+      <c r="G86" t="n">
         <v>416.83</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="3">
+      <c r="H86" t="n">
+        <v>168.8422383143539</v>
+      </c>
+      <c r="I86" t="n">
+        <v>152.93232240375</v>
+      </c>
+      <c r="J86" t="n">
+        <v>167.2285247091908</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1782.018545855899</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1097.522090320234</v>
+      </c>
+      <c r="M86" t="n">
+        <v>246.8754288982698</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3126.416065074402</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B87" s="4">
+      <c r="C87" t="n">
         <v>6988.42</v>
       </c>
-      <c r="C87" s="4">
+      <c r="D87" t="n">
         <v>2363.9</v>
       </c>
-      <c r="D87" s="4">
+      <c r="E87" t="n">
         <v>2539.91</v>
       </c>
-      <c r="E87" s="4">
+      <c r="F87" t="n">
         <v>1709.27</v>
       </c>
-      <c r="F87" s="4">
+      <c r="G87" t="n">
         <v>375.34</v>
+      </c>
+      <c r="H87" t="n">
+        <v>172.1346619614838</v>
+      </c>
+      <c r="I87" t="n">
+        <v>153.8652095704129</v>
+      </c>
+      <c r="J87" t="n">
+        <v>171.124949334915</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1373.285294816995</v>
+      </c>
+      <c r="L87" t="n">
+        <v>998.8432467873076</v>
+      </c>
+      <c r="M87" t="n">
+        <v>218.0502147115406</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2590.178756315843</v>
       </c>
     </row>
   </sheetData>
